--- a/data_lake/macro/South Korea/Retail Sales.xlsx
+++ b/data_lake/macro/South Korea/Retail Sales.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\South Korea\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\South Korea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D919DD-671B-4562-96E9-C85B42054F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDCAA9E3-8EB8-4A43-9D7A-96DF7925757C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="KORSLM" sheetId="1" r:id="rId1"/>
+    <sheet name="info" sheetId="2" r:id="rId1"/>
+    <sheet name="KORSLM" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="19">
   <si>
     <t>Release date</t>
   </si>
@@ -59,20 +60,71 @@
   <si>
     <t>UTC+9</t>
   </si>
+  <si>
+    <t>https://kr.investing.com/economic-calendar/south-korean-retail-sales-474</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ticker</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>URL</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frequency</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exchange</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Country</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>South Korea</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>KSTAT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monthly</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>KORSLM</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="171" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -80,9 +132,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -93,7 +178,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -101,38 +186,68 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="백분율" xfId="1" builtinId="5"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -409,4258 +524,4348 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I193"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAFA9428-CE82-4463-B6D6-94A9ACDD19FC}">
+  <dimension ref="B2:G3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.796875" style="5"/>
+    <col min="3" max="3" width="7.69921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.59765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.69921875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.8984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.796875" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="13">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{8F9536AD-93CA-4EE8-A83B-ADDABA30CDC4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I194"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.296875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.796875" style="11"/>
+    <col min="8" max="8" width="8.796875" style="5"/>
+    <col min="9" max="9" width="9.59765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.796875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2" s="6">
         <v>40330</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="6">
         <v>40389</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1">
+      <c r="D2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="11">
         <v>2.4E-2</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="11">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="I2" s="2"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="6">
         <v>40360</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="6">
         <v>40421</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="7">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="D3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="11">
         <v>1.2E-2</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="11">
         <v>2.4E-2</v>
       </c>
-      <c r="I3" s="2"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="6">
         <v>40391</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="6">
         <v>40451</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="D4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="11">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="11">
         <v>1.4E-2</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="11">
         <v>1.2E-2</v>
       </c>
-      <c r="I4" s="2"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="6">
         <v>40422</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="6">
         <v>40480</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
         <v>0.44791666666666669</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="11">
         <v>1E-3</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="11">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="I5" s="2"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6" s="6">
         <v>40452</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="6">
         <v>40512</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>0.375</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="11">
         <v>2E-3</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="11">
         <v>1E-3</v>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="A7" s="6">
         <v>40483</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="6">
         <v>40542</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>0.375</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="11">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="11">
         <v>1E-3</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="11">
         <v>2E-3</v>
       </c>
-      <c r="I7" s="2"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="A8" s="6">
         <v>40513</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="6">
         <v>40574</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="D8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="11">
         <v>-0.01</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="11">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="I8" s="2"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="A9" s="6">
         <v>40544</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="6">
         <v>40605</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>0.375</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="11">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="11">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="I9" s="2"/>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+      <c r="A10" s="6">
         <v>40575</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="6">
         <v>40633</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="11">
         <v>-6.0999999999999999E-2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="11">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="I10" s="2"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="A11" s="6">
         <v>40603</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="6">
         <v>40662</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>0.38541666666666669</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="D11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="11">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="11">
         <v>0.04</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="11">
         <v>-6.2E-2</v>
       </c>
-      <c r="I11" s="2"/>
+      <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="A12" s="6">
         <v>40634</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="6">
         <v>40694</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="D12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="11">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="11">
         <v>1E-3</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="11">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="I12" s="2"/>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="A13" s="6">
         <v>40664</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="6">
         <v>40724</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>0.375</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="D13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="11">
         <v>0.01</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="11">
         <v>-0.01</v>
       </c>
-      <c r="I13" s="2"/>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="A14" s="6">
         <v>40695</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="6">
         <v>40753</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="1">
+      <c r="D14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="11">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="11">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="11">
         <v>0.01</v>
       </c>
-      <c r="I14" s="2"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="A15" s="6">
         <v>40725</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="6">
         <v>40786</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>0.375</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="D15" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="11">
         <v>2.3E-2</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="11">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="11">
         <v>1.4E-2</v>
       </c>
-      <c r="I15" s="2"/>
+      <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="A16" s="6">
         <v>40756</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="6">
         <v>40816</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <v>0.375</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="D16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="11">
         <v>2.3E-2</v>
       </c>
-      <c r="I16" s="2"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+      <c r="A17" s="6">
         <v>40787</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="6">
         <v>40847</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <v>0.375</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="D17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="11">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="I17" s="2"/>
+      <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+      <c r="A18" s="6">
         <v>40817</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="6">
         <v>40877</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="7">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="D18" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="11">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="I18" s="2"/>
+      <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
+      <c r="A19" s="6">
         <v>40848</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="6">
         <v>40906</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="7">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="1">
+      <c r="D19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="11">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I19" s="2"/>
+      <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="A20" s="6">
         <v>40878</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="6">
         <v>40939</v>
       </c>
-      <c r="C20" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="1">
+      <c r="C20" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="11">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="I20" s="2"/>
+      <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
+      <c r="A21" s="6">
         <v>40909</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="6">
         <v>40968</v>
       </c>
-      <c r="C21" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="1">
+      <c r="C21" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="11">
         <v>-0.02</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="11">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="I21" s="2"/>
+      <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="A22" s="6">
         <v>40940</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="6">
         <v>40998</v>
       </c>
-      <c r="C22" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="1">
+      <c r="C22" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="11">
         <v>-0.01</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="I22" s="2"/>
+      <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+      <c r="A23" s="6">
         <v>40969</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="6">
         <v>41029</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="1">
+      <c r="D23" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="11">
         <v>-2.7E-2</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="11">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="I23" s="2"/>
+      <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="A24" s="6">
         <v>41000</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="6">
         <v>41060</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="D24" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="11">
         <v>0.01</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="11">
         <v>0.01</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="11">
         <v>-2.7E-2</v>
       </c>
-      <c r="I24" s="2"/>
+      <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+      <c r="A25" s="6">
         <v>41030</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="6">
         <v>41089</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D25" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="11">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="I25" s="2"/>
+      <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+      <c r="A26" s="6">
         <v>41061</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="6">
         <v>41121</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="D26" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="11">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="I26" s="2"/>
+      <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+      <c r="A27" s="6">
         <v>41091</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="6">
         <v>41152</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="D27" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="11">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="I27" s="2"/>
+      <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+      <c r="A28" s="6">
         <v>41122</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="6">
         <v>41180</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="1">
+      <c r="D28" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="11">
         <v>-0.03</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="11">
         <v>0.01</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="11">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="I28" s="2"/>
+      <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
+      <c r="A29" s="6">
         <v>41153</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="6">
         <v>41213</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="1">
+      <c r="D29" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="11">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="11">
         <v>0.02</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="11">
         <v>-3.1E-2</v>
       </c>
-      <c r="I29" s="2"/>
+      <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+      <c r="A30" s="6">
         <v>41183</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="6">
         <v>41243</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="D30" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="11">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="11">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="I30" s="2"/>
+      <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
+      <c r="A31" s="6">
         <v>41214</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="6">
         <v>41271</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="D31" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="11">
         <v>2.3E-2</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" s="11">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="I31" s="2"/>
+      <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
+      <c r="A32" s="6">
         <v>41244</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="6">
         <v>41305</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D32" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="11">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="11">
         <v>-0.01</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" s="11">
         <v>2.3E-2</v>
       </c>
-      <c r="I32" s="2"/>
+      <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
+      <c r="A33" s="6">
         <v>41275</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="6">
         <v>41333</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="D33" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="11">
         <v>-0.02</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="I33" s="2"/>
+      <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
+      <c r="A34" s="6">
         <v>41306</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="6">
         <v>41362</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="D34" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="11">
         <v>0.01</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="11">
         <v>-2.1999999999999999E-2</v>
       </c>
-      <c r="I34" s="2"/>
+      <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
+      <c r="A35" s="6">
         <v>41334</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="6">
         <v>41394</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D35" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" s="11">
         <v>1.4E-2</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" s="11">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="I35" s="2"/>
+      <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
+      <c r="A36" s="6">
         <v>41365</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="6">
         <v>41425</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="D36" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" s="11">
         <v>1.6E-2</v>
       </c>
-      <c r="I36" s="2"/>
+      <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
+      <c r="A37" s="6">
         <v>41395</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="6">
         <v>41453</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D37" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="I37" s="2"/>
+      <c r="I37" s="4"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="3">
+      <c r="A38" s="6">
         <v>41426</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="6">
         <v>41485</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D38" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D38" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="11">
         <v>1E-3</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="I38" s="2"/>
+      <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
+      <c r="A39" s="6">
         <v>41456</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="6">
         <v>41516</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D39" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="11">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G39" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="I39" s="2"/>
+      <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
+      <c r="A40" s="6">
         <v>41487</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="6">
         <v>41547</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="7">
         <v>0.4375</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D40" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="11">
         <v>0</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" s="11">
         <v>1.2E-2</v>
       </c>
-      <c r="I40" s="2"/>
+      <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
+      <c r="A41" s="6">
         <v>41518</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="6">
         <v>41577</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="7">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D41" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="D41" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="11">
         <v>-0.02</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I41" s="2"/>
+      <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
+      <c r="A42" s="6">
         <v>41548</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="6">
         <v>41608</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="7">
         <v>0.35416666666666669</v>
       </c>
-      <c r="D42" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D42" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="11">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" s="11">
         <v>-0.02</v>
       </c>
-      <c r="I42" s="2"/>
+      <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
+      <c r="A43" s="6">
         <v>41579</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="6">
         <v>41638</v>
       </c>
-      <c r="C43" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="C43" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G43" s="11">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="I43" s="2"/>
+      <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
+      <c r="A44" s="6">
         <v>41609</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="6">
         <v>41668</v>
       </c>
-      <c r="C44" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="C44" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="11">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G44" s="1">
+      <c r="G44" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="I44" s="2"/>
+      <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="3">
+      <c r="A45" s="6">
         <v>41640</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="6">
         <v>41698</v>
       </c>
-      <c r="C45" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="C45" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="11">
         <v>2.4E-2</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G45" s="1">
+      <c r="G45" s="11">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="I45" s="2"/>
+      <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="3">
+      <c r="A46" s="6">
         <v>41671</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="6">
         <v>41726</v>
       </c>
-      <c r="C46" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="C46" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="11">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G46" s="11">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="I46" s="2"/>
+      <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="3">
+      <c r="A47" s="6">
         <v>41699</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="6">
         <v>41759</v>
       </c>
-      <c r="C47" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="C47" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="11">
         <v>1.6E-2</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G47" s="1">
+      <c r="G47" s="11">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="I47" s="2"/>
+      <c r="I47" s="4"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="3">
+      <c r="A48" s="6">
         <v>41730</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="6">
         <v>41789</v>
       </c>
-      <c r="C48" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="1">
+      <c r="C48" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="11">
         <v>-1.7000000000000001E-2</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G48" s="1">
+      <c r="G48" s="11">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="I48" s="2"/>
+      <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="3">
+      <c r="A49" s="6">
         <v>41760</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="6">
         <v>41817</v>
       </c>
-      <c r="C49" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="1">
+      <c r="C49" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="11">
         <v>1.4E-2</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="11">
         <v>0.01</v>
       </c>
-      <c r="G49" s="1">
+      <c r="G49" s="11">
         <v>-1.6E-2</v>
       </c>
-      <c r="I49" s="2"/>
+      <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
+      <c r="A50" s="6">
         <v>41791</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="6">
         <v>41850</v>
       </c>
-      <c r="C50" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="1">
+      <c r="C50" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G50" s="1">
+      <c r="G50" s="11">
         <v>1.4E-2</v>
       </c>
-      <c r="I50" s="2"/>
+      <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
+      <c r="A51" s="6">
         <v>41821</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="6">
         <v>41880</v>
       </c>
-      <c r="C51" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="1">
+      <c r="C51" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G51" s="1">
+      <c r="G51" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I51" s="2"/>
+      <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="3">
+      <c r="A52" s="6">
         <v>41852</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="6">
         <v>41912</v>
       </c>
-      <c r="C52" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" s="1">
+      <c r="C52" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="11">
         <v>2.7E-2</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G52" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I52" s="2"/>
+      <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="3">
+      <c r="A53" s="6">
         <v>41883</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="6">
         <v>41942</v>
       </c>
-      <c r="C53" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" s="1">
+      <c r="C53" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="11">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G53" s="11">
         <v>2.7E-2</v>
       </c>
-      <c r="I53" s="2"/>
+      <c r="I53" s="4"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="3">
+      <c r="A54" s="6">
         <v>41913</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="6">
         <v>41971</v>
       </c>
-      <c r="C54" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" s="1">
+      <c r="C54" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" s="11">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G54" s="11">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="I54" s="2"/>
+      <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="3">
+      <c r="A55" s="6">
         <v>41944</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="6">
         <v>42003</v>
       </c>
-      <c r="C55" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" s="1">
+      <c r="C55" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="11">
         <v>1.9E-2</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G55" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="I55" s="2"/>
+      <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="3">
+      <c r="A56" s="6">
         <v>41974</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="6">
         <v>42034</v>
       </c>
-      <c r="C56" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" s="1">
+      <c r="C56" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="11">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G56" s="11">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="I56" s="2"/>
+      <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" s="3">
+      <c r="A57" s="6">
         <v>42005</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="6">
         <v>42065</v>
       </c>
-      <c r="C57" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="1">
+      <c r="C57" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="11">
         <v>-3.1E-2</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G57" s="11">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="I57" s="2"/>
+      <c r="I57" s="4"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" s="3">
+      <c r="A58" s="6">
         <v>42036</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="6">
         <v>42094</v>
       </c>
-      <c r="C58" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="C58" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="11">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G58" s="11">
         <v>-2.8000000000000001E-2</v>
       </c>
-      <c r="I58" s="2"/>
+      <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="3">
+      <c r="A59" s="6">
         <v>42064</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="6">
         <v>42124</v>
       </c>
-      <c r="C59" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" s="1">
+      <c r="C59" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="11">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="11">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" s="11">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="I59" s="2"/>
+      <c r="I59" s="4"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" s="3">
+      <c r="A60" s="6">
         <v>42095</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="6">
         <v>42153</v>
       </c>
-      <c r="C60" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" s="1">
+      <c r="C60" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" s="11">
         <v>1.6E-2</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G60" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="I60" s="2"/>
+      <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="3">
+      <c r="A61" s="6">
         <v>42125</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="6">
         <v>42185</v>
       </c>
-      <c r="C61" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="C61" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="11">
         <v>0</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G61" s="11">
         <v>1.4E-2</v>
       </c>
-      <c r="I61" s="2"/>
+      <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="3">
+      <c r="A62" s="6">
         <v>42156</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="6">
         <v>42216</v>
       </c>
-      <c r="C62" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E62" s="1">
+      <c r="C62" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="11">
         <v>-3.6999999999999998E-2</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="G62" s="1">
+      <c r="G62" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="I62" s="2"/>
+      <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="3">
+      <c r="A63" s="6">
         <v>42186</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="6">
         <v>42247</v>
       </c>
-      <c r="C63" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="1">
+      <c r="C63" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" s="11">
         <v>1.9E-2</v>
       </c>
-      <c r="G63" s="1">
+      <c r="G63" s="11">
         <v>-3.5000000000000003E-2</v>
       </c>
-      <c r="I63" s="2"/>
+      <c r="I63" s="4"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="3">
+      <c r="A64" s="6">
         <v>42217</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="6">
         <v>42278</v>
       </c>
-      <c r="C64" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="1">
+      <c r="C64" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" s="11">
         <v>1.9E-2</v>
       </c>
-      <c r="G64" s="1">
+      <c r="G64" s="11">
         <v>0.02</v>
       </c>
-      <c r="I64" s="2"/>
+      <c r="I64" s="4"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="3">
+      <c r="A65" s="6">
         <v>42248</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="6">
         <v>42307</v>
       </c>
-      <c r="C65" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" s="1">
+      <c r="C65" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G65" s="1">
+      <c r="G65" s="11">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="I65" s="2"/>
+      <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="3">
+      <c r="A66" s="6">
         <v>42278</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="6">
         <v>42338</v>
       </c>
-      <c r="C66" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E66" s="1">
+      <c r="C66" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" s="11">
         <v>3.1E-2</v>
       </c>
-      <c r="G66" s="1">
+      <c r="G66" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I66" s="2"/>
+      <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="3">
+      <c r="A67" s="6">
         <v>42309</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="6">
         <v>42368</v>
       </c>
-      <c r="C67" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" s="1">
+      <c r="C67" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" s="11">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="G67" s="1">
+      <c r="G67" s="11">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="I67" s="2"/>
+      <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" s="3">
+      <c r="A68" s="6">
         <v>42339</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="6">
         <v>42398</v>
       </c>
-      <c r="C68" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E68" s="1">
+      <c r="C68" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="G68" s="1">
+      <c r="G68" s="11">
         <v>-0.01</v>
       </c>
-      <c r="I68" s="2"/>
+      <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" s="3">
+      <c r="A69" s="6">
         <v>42370</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="6">
         <v>42431</v>
       </c>
-      <c r="C69" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E69" s="1">
+      <c r="C69" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E69" s="11">
         <v>-1.4E-2</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G69" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="I69" s="2"/>
+      <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" s="3">
+      <c r="A70" s="6">
         <v>42401</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="6">
         <v>42460</v>
       </c>
-      <c r="C70" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E70" s="1">
+      <c r="C70" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" s="11">
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="G70" s="1">
+      <c r="G70" s="11">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="I70" s="2"/>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="3">
+      <c r="A71" s="6">
         <v>42430</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="6">
         <v>42489</v>
       </c>
-      <c r="C71" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E71" s="1">
+      <c r="C71" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" s="11">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G71" s="11">
         <v>-1.4999999999999999E-2</v>
       </c>
-      <c r="I71" s="2"/>
+      <c r="I71" s="4"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="3">
+      <c r="A72" s="6">
         <v>42461</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="6">
         <v>42521</v>
       </c>
-      <c r="C72" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" s="1">
+      <c r="C72" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G72" s="11">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="I72" s="2"/>
+      <c r="I72" s="4"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" s="3">
+      <c r="A73" s="6">
         <v>42491</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="6">
         <v>42551</v>
       </c>
-      <c r="C73" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E73" s="1">
+      <c r="C73" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G73" s="1">
+      <c r="G73" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="I73" s="2"/>
+      <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" s="3">
+      <c r="A74" s="6">
         <v>42522</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="6">
         <v>42580</v>
       </c>
-      <c r="C74" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" s="1">
+      <c r="C74" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" s="11">
         <v>0.01</v>
       </c>
-      <c r="G74" s="1">
+      <c r="G74" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I74" s="2"/>
+      <c r="I74" s="4"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" s="3">
+      <c r="A75" s="6">
         <v>42552</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75" s="6">
         <v>42613</v>
       </c>
-      <c r="C75" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" s="1">
+      <c r="C75" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="11">
         <v>-2.5999999999999999E-2</v>
       </c>
-      <c r="G75" s="1">
+      <c r="G75" s="11">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="I75" s="2"/>
+      <c r="I75" s="4"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" s="3">
+      <c r="A76" s="6">
         <v>42583</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="6">
         <v>42643</v>
       </c>
-      <c r="C76" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" s="1">
+      <c r="C76" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" s="11">
         <v>0.02</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G76" s="11">
         <v>-2.5999999999999999E-2</v>
       </c>
-      <c r="I76" s="2"/>
+      <c r="I76" s="4"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" s="3">
+      <c r="A77" s="6">
         <v>42614</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77" s="6">
         <v>42674</v>
       </c>
-      <c r="C77" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E77" s="1">
+      <c r="C77" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" s="11">
         <v>-4.4999999999999998E-2</v>
       </c>
-      <c r="G77" s="1">
+      <c r="G77" s="11">
         <v>0.02</v>
       </c>
-      <c r="I77" s="2"/>
+      <c r="I77" s="4"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" s="3">
+      <c r="A78" s="6">
         <v>42644</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="6">
         <v>42704</v>
       </c>
-      <c r="C78" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E78" s="1">
+      <c r="C78" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" s="11">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="G78" s="1">
+      <c r="G78" s="11">
         <v>-4.4999999999999998E-2</v>
       </c>
-      <c r="I78" s="2"/>
+      <c r="I78" s="4"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="3">
+      <c r="A79" s="6">
         <v>42675</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79" s="6">
         <v>42733</v>
       </c>
-      <c r="C79" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E79" s="1">
+      <c r="C79" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E79" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="G79" s="1">
+      <c r="G79" s="11">
         <v>5.5E-2</v>
       </c>
-      <c r="I79" s="2"/>
+      <c r="I79" s="4"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="3">
+      <c r="A80" s="6">
         <v>42705</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80" s="6">
         <v>42767</v>
       </c>
-      <c r="C80" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E80" s="1">
+      <c r="C80" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" s="11">
         <v>-1.2E-2</v>
       </c>
-      <c r="G80" s="1">
+      <c r="G80" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="I80" s="2"/>
+      <c r="I80" s="4"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" s="3">
+      <c r="A81" s="6">
         <v>42736</v>
       </c>
-      <c r="B81" s="3">
+      <c r="B81" s="6">
         <v>42796</v>
       </c>
-      <c r="C81" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" s="1">
+      <c r="C81" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" s="11">
         <v>-2.1999999999999999E-2</v>
       </c>
-      <c r="G81" s="1">
+      <c r="G81" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="I81" s="2"/>
+      <c r="I81" s="4"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A82" s="3">
+      <c r="A82" s="6">
         <v>42767</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82" s="6">
         <v>42825</v>
       </c>
-      <c r="C82" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" s="1">
+      <c r="C82" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="11">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="G82" s="1">
+      <c r="G82" s="11">
         <v>-0.02</v>
       </c>
-      <c r="I82" s="2"/>
+      <c r="I82" s="4"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83" s="3">
+      <c r="A83" s="6">
         <v>42795</v>
       </c>
-      <c r="B83" s="3">
+      <c r="B83" s="6">
         <v>42853</v>
       </c>
-      <c r="C83" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E83" s="1">
+      <c r="C83" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E83" s="11">
         <v>0</v>
       </c>
-      <c r="G83" s="1">
+      <c r="G83" s="11">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="I83" s="2"/>
+      <c r="I83" s="4"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A84" s="3">
+      <c r="A84" s="6">
         <v>42826</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84" s="6">
         <v>42886</v>
       </c>
-      <c r="C84" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E84" s="1">
+      <c r="C84" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E84" s="11">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G84" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="I84" s="2"/>
+      <c r="I84" s="4"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A85" s="3">
+      <c r="A85" s="6">
         <v>42856</v>
       </c>
-      <c r="B85" s="3">
+      <c r="B85" s="6">
         <v>42916</v>
       </c>
-      <c r="C85" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E85" s="1">
+      <c r="C85" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" s="11">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G85" s="11">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="I85" s="2"/>
+      <c r="I85" s="4"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A86" s="3">
+      <c r="A86" s="6">
         <v>42887</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86" s="6">
         <v>42944</v>
       </c>
-      <c r="C86" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E86" s="1">
+      <c r="C86" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" s="11">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="G86" s="1">
+      <c r="G86" s="11">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="I86" s="2"/>
+      <c r="I86" s="4"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A87" s="3">
+      <c r="A87" s="6">
         <v>42917</v>
       </c>
-      <c r="B87" s="3">
+      <c r="B87" s="6">
         <v>42978</v>
       </c>
-      <c r="C87" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E87" s="1">
+      <c r="C87" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G87" s="1">
+      <c r="G87" s="11">
         <v>1.2E-2</v>
       </c>
-      <c r="I87" s="2"/>
+      <c r="I87" s="4"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A88" s="3">
+      <c r="A88" s="6">
         <v>42948</v>
       </c>
-      <c r="B88" s="3">
+      <c r="B88" s="6">
         <v>43007</v>
       </c>
-      <c r="C88" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E88" s="1">
+      <c r="C88" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E88" s="11">
         <v>-0.01</v>
       </c>
-      <c r="G88" s="1">
+      <c r="G88" s="11">
         <v>1E-3</v>
       </c>
-      <c r="I88" s="2"/>
+      <c r="I88" s="4"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A89" s="3">
+      <c r="A89" s="6">
         <v>42979</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B89" s="6">
         <v>43039</v>
       </c>
-      <c r="C89" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E89" s="1">
+      <c r="C89" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E89" s="11">
         <v>3.1E-2</v>
       </c>
-      <c r="G89" s="1">
+      <c r="G89" s="11">
         <v>-0.01</v>
       </c>
-      <c r="I89" s="2"/>
+      <c r="I89" s="4"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A90" s="3">
+      <c r="A90" s="6">
         <v>43009</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90" s="6">
         <v>43069</v>
       </c>
-      <c r="C90" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E90" s="1">
+      <c r="C90" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E90" s="11">
         <v>-2.9000000000000001E-2</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G90" s="11">
         <v>3.1E-2</v>
       </c>
-      <c r="I90" s="2"/>
+      <c r="I90" s="4"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A91" s="3">
+      <c r="A91" s="6">
         <v>43040</v>
       </c>
-      <c r="B91" s="3">
+      <c r="B91" s="6">
         <v>43097</v>
       </c>
-      <c r="C91" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E91" s="1">
+      <c r="C91" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" s="11">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G91" s="11">
         <v>-2.9000000000000001E-2</v>
       </c>
-      <c r="I91" s="2"/>
+      <c r="I91" s="4"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A92" s="3">
+      <c r="A92" s="6">
         <v>43070</v>
       </c>
-      <c r="B92" s="3">
+      <c r="B92" s="6">
         <v>43131</v>
       </c>
-      <c r="C92" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E92" s="1">
+      <c r="C92" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E92" s="11">
         <v>-0.04</v>
       </c>
-      <c r="G92" s="1">
+      <c r="G92" s="11">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="I92" s="2"/>
+      <c r="I92" s="4"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A93" s="3">
+      <c r="A93" s="6">
         <v>43101</v>
       </c>
-      <c r="B93" s="3">
+      <c r="B93" s="6">
         <v>43161</v>
       </c>
-      <c r="C93" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E93" s="1">
+      <c r="C93" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E93" s="11">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="G93" s="1">
+      <c r="G93" s="11">
         <v>-2.5999999999999999E-2</v>
       </c>
-      <c r="I93" s="2"/>
+      <c r="I93" s="4"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A94" s="3">
+      <c r="A94" s="6">
         <v>43132</v>
       </c>
-      <c r="B94" s="3">
+      <c r="B94" s="6">
         <v>43189</v>
       </c>
-      <c r="C94" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E94" s="1">
+      <c r="C94" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E94" s="11">
         <v>0.01</v>
       </c>
-      <c r="G94" s="1">
+      <c r="G94" s="11">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="I94" s="2"/>
+      <c r="I94" s="4"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="3">
+      <c r="A95" s="6">
         <v>43160</v>
       </c>
-      <c r="B95" s="3">
+      <c r="B95" s="6">
         <v>43220</v>
       </c>
-      <c r="C95" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E95" s="1">
+      <c r="C95" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" s="11">
         <v>2.7E-2</v>
       </c>
-      <c r="G95" s="1">
+      <c r="G95" s="11">
         <v>0.01</v>
       </c>
-      <c r="I95" s="2"/>
+      <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="3">
+      <c r="A96" s="6">
         <v>43191</v>
       </c>
-      <c r="B96" s="3">
+      <c r="B96" s="6">
         <v>43251</v>
       </c>
-      <c r="C96" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E96" s="1">
+      <c r="C96" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" s="11">
         <v>-0.01</v>
       </c>
-      <c r="G96" s="1">
+      <c r="G96" s="11">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="I96" s="2"/>
+      <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A97" s="3">
+      <c r="A97" s="6">
         <v>43221</v>
       </c>
-      <c r="B97" s="3">
+      <c r="B97" s="6">
         <v>43280</v>
       </c>
-      <c r="C97" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E97" s="1">
+      <c r="C97" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E97" s="11">
         <v>-0.01</v>
       </c>
-      <c r="G97" s="1">
+      <c r="G97" s="11">
         <v>-0.01</v>
       </c>
-      <c r="I97" s="2"/>
+      <c r="I97" s="4"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A98" s="3">
+      <c r="A98" s="6">
         <v>43252</v>
       </c>
-      <c r="B98" s="3">
+      <c r="B98" s="6">
         <v>43312</v>
       </c>
-      <c r="C98" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E98" s="1">
+      <c r="C98" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G98" s="11">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="I98" s="2"/>
+      <c r="I98" s="4"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A99" s="3">
+      <c r="A99" s="6">
         <v>43282</v>
       </c>
-      <c r="B99" s="3">
+      <c r="B99" s="6">
         <v>43343</v>
       </c>
-      <c r="C99" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E99" s="1">
+      <c r="C99" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E99" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G99" s="11">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="I99" s="2"/>
+      <c r="I99" s="4"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A100" s="3">
+      <c r="A100" s="6">
         <v>43313</v>
       </c>
-      <c r="B100" s="3">
+      <c r="B100" s="6">
         <v>43375</v>
       </c>
-      <c r="C100" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E100" s="1">
+      <c r="C100" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E100" s="11">
         <v>1.4E-2</v>
       </c>
-      <c r="G100" s="1">
+      <c r="G100" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I100" s="2"/>
+      <c r="I100" s="4"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="3">
+      <c r="A101" s="6">
         <v>43344</v>
       </c>
-      <c r="B101" s="3">
+      <c r="B101" s="6">
         <v>43404</v>
       </c>
-      <c r="C101" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E101" s="1">
+      <c r="C101" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" s="11">
         <v>-2.5000000000000001E-2</v>
       </c>
-      <c r="G101" s="1">
+      <c r="G101" s="11">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="I101" s="2"/>
+      <c r="I101" s="4"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="3">
+      <c r="A102" s="6">
         <v>43374</v>
       </c>
-      <c r="B102" s="3">
+      <c r="B102" s="6">
         <v>43434</v>
       </c>
-      <c r="C102" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E102" s="1">
+      <c r="C102" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G102" s="1">
+      <c r="G102" s="11">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="I102" s="2"/>
+      <c r="I102" s="4"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" s="3">
+      <c r="A103" s="6">
         <v>43405</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B103" s="6">
         <v>43462</v>
       </c>
-      <c r="C103" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E103" s="1">
+      <c r="C103" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G103" s="1">
+      <c r="G103" s="11">
         <v>2E-3</v>
       </c>
-      <c r="I103" s="2"/>
+      <c r="I103" s="4"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" s="3">
+      <c r="A104" s="6">
         <v>43435</v>
       </c>
-      <c r="B104" s="3">
+      <c r="B104" s="6">
         <v>43496</v>
       </c>
-      <c r="C104" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E104" s="1">
+      <c r="C104" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E104" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G104" s="1">
+      <c r="G104" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="I104" s="2"/>
+      <c r="I104" s="4"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" s="3">
+      <c r="A105" s="6">
         <v>43466</v>
       </c>
-      <c r="B105" s="3">
+      <c r="B105" s="6">
         <v>43524</v>
       </c>
-      <c r="C105" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E105" s="1">
+      <c r="C105" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E105" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G105" s="1">
+      <c r="G105" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="I105" s="2"/>
+      <c r="I105" s="4"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" s="3">
+      <c r="A106" s="6">
         <v>43497</v>
       </c>
-      <c r="B106" s="3">
+      <c r="B106" s="6">
         <v>43553</v>
       </c>
-      <c r="C106" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E106" s="1">
+      <c r="C106" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E106" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="G106" s="1">
+      <c r="G106" s="11">
         <v>1E-3</v>
       </c>
-      <c r="I106" s="2"/>
+      <c r="I106" s="4"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" s="3">
+      <c r="A107" s="6">
         <v>43525</v>
       </c>
-      <c r="B107" s="3">
+      <c r="B107" s="6">
         <v>43585</v>
       </c>
-      <c r="C107" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D107" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E107" s="1">
+      <c r="C107" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E107" s="11">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="G107" s="1">
+      <c r="G107" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="I107" s="2"/>
+      <c r="I107" s="4"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" s="3">
+      <c r="A108" s="6">
         <v>43556</v>
       </c>
-      <c r="B108" s="3">
+      <c r="B108" s="6">
         <v>43616</v>
       </c>
-      <c r="C108" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E108" s="1">
+      <c r="C108" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E108" s="11">
         <v>-1.2E-2</v>
       </c>
-      <c r="G108" s="1">
+      <c r="G108" s="11">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="I108" s="2"/>
+      <c r="I108" s="4"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="3">
+      <c r="A109" s="6">
         <v>43586</v>
       </c>
-      <c r="B109" s="3">
+      <c r="B109" s="6">
         <v>43644</v>
       </c>
-      <c r="C109" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E109" s="1">
+      <c r="C109" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E109" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="G109" s="1">
+      <c r="G109" s="11">
         <v>-1.2E-2</v>
       </c>
-      <c r="I109" s="2"/>
+      <c r="I109" s="4"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A110" s="3">
+      <c r="A110" s="6">
         <v>43617</v>
       </c>
-      <c r="B110" s="3">
+      <c r="B110" s="6">
         <v>43677</v>
       </c>
-      <c r="C110" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E110" s="1">
+      <c r="C110" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E110" s="11">
         <v>-1.6E-2</v>
       </c>
-      <c r="G110" s="1">
+      <c r="G110" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="I110" s="2"/>
+      <c r="I110" s="4"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" s="3">
+      <c r="A111" s="6">
         <v>43647</v>
       </c>
-      <c r="B111" s="3">
+      <c r="B111" s="6">
         <v>43707</v>
       </c>
-      <c r="C111" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E111" s="1">
+      <c r="C111" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E111" s="11">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="G111" s="1">
+      <c r="G111" s="11">
         <v>-1.6E-2</v>
       </c>
-      <c r="I111" s="2"/>
+      <c r="I111" s="4"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" s="3">
+      <c r="A112" s="6">
         <v>43678</v>
       </c>
-      <c r="B112" s="3">
+      <c r="B112" s="6">
         <v>43738</v>
       </c>
-      <c r="C112" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E112" s="1">
+      <c r="C112" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E112" s="11">
         <v>3.9E-2</v>
       </c>
-      <c r="G112" s="1">
+      <c r="G112" s="11">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="I112" s="2"/>
+      <c r="I112" s="4"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A113" s="3">
+      <c r="A113" s="6">
         <v>43709</v>
       </c>
-      <c r="B113" s="3">
+      <c r="B113" s="6">
         <v>43769</v>
       </c>
-      <c r="C113" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E113" s="1">
+      <c r="C113" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E113" s="11">
         <v>-2.1999999999999999E-2</v>
       </c>
-      <c r="G113" s="1">
+      <c r="G113" s="11">
         <v>3.9E-2</v>
       </c>
-      <c r="I113" s="2"/>
+      <c r="I113" s="4"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A114" s="3">
+      <c r="A114" s="6">
         <v>43739</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114" s="6">
         <v>43798</v>
       </c>
-      <c r="C114" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E114" s="1">
+      <c r="C114" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E114" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="G114" s="1">
+      <c r="G114" s="11">
         <v>-2.1999999999999999E-2</v>
       </c>
-      <c r="I114" s="2"/>
+      <c r="I114" s="4"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A115" s="3">
+      <c r="A115" s="6">
         <v>43770</v>
       </c>
-      <c r="B115" s="3">
+      <c r="B115" s="6">
         <v>43829</v>
       </c>
-      <c r="C115" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E115" s="1">
+      <c r="C115" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E115" s="11">
         <v>0.03</v>
       </c>
-      <c r="G115" s="1">
+      <c r="G115" s="11">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="I115" s="2"/>
+      <c r="I115" s="4"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A116" s="3">
+      <c r="A116" s="6">
         <v>43800</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116" s="6">
         <v>43861</v>
       </c>
-      <c r="C116" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E116" s="1">
+      <c r="C116" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E116" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="G116" s="1">
+      <c r="G116" s="11">
         <v>0.03</v>
       </c>
-      <c r="I116" s="2"/>
+      <c r="I116" s="4"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A117" s="3">
+      <c r="A117" s="6">
         <v>43831</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117" s="6">
         <v>43889</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="7">
         <v>0.25</v>
       </c>
-      <c r="D117" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E117" s="1">
+      <c r="D117" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E117" s="11">
         <v>-3.1E-2</v>
       </c>
-      <c r="G117" s="1">
+      <c r="G117" s="11">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I117" s="2"/>
+      <c r="I117" s="4"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A118" s="3">
+      <c r="A118" s="6">
         <v>43862</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118" s="6">
         <v>43921</v>
       </c>
-      <c r="C118" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E118" s="1">
+      <c r="C118" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E118" s="11">
         <v>-0.06</v>
       </c>
-      <c r="G118" s="1">
+      <c r="G118" s="11">
         <v>-3.1E-2</v>
       </c>
-      <c r="I118" s="2"/>
+      <c r="I118" s="4"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A119" s="3">
+      <c r="A119" s="6">
         <v>43891</v>
       </c>
-      <c r="B119" s="3">
+      <c r="B119" s="6">
         <v>43950</v>
       </c>
-      <c r="C119" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E119" s="1">
+      <c r="C119" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E119" s="11">
         <v>-0.01</v>
       </c>
-      <c r="G119" s="1">
+      <c r="G119" s="11">
         <v>-0.06</v>
       </c>
-      <c r="I119" s="2"/>
+      <c r="I119" s="4"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A120" s="3">
+      <c r="A120" s="6">
         <v>43922</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120" s="6">
         <v>43980</v>
       </c>
-      <c r="C120" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E120" s="1">
+      <c r="C120" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E120" s="11">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="G120" s="1">
+      <c r="G120" s="11">
         <v>-0.01</v>
       </c>
-      <c r="I120" s="2"/>
+      <c r="I120" s="4"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A121" s="3">
+      <c r="A121" s="6">
         <v>43952</v>
       </c>
-      <c r="B121" s="3">
+      <c r="B121" s="6">
         <v>44012</v>
       </c>
-      <c r="C121" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E121" s="1">
+      <c r="C121" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E121" s="11">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="G121" s="1">
+      <c r="G121" s="11">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="I121" s="2"/>
+      <c r="I121" s="4"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A122" s="3">
+      <c r="A122" s="6">
         <v>43983</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122" s="6">
         <v>44043</v>
       </c>
-      <c r="C122" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E122" s="1">
+      <c r="C122" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E122" s="11">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="G122" s="1">
+      <c r="G122" s="11">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="I122" s="2"/>
+      <c r="I122" s="4"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A123" s="3">
+      <c r="A123" s="6">
         <v>44013</v>
       </c>
-      <c r="B123" s="3">
+      <c r="B123" s="6">
         <v>44074</v>
       </c>
-      <c r="C123" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E123" s="1">
+      <c r="C123" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E123" s="11">
         <v>-0.06</v>
       </c>
-      <c r="G123" s="1">
+      <c r="G123" s="11">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="I123" s="2"/>
+      <c r="I123" s="4"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A124" s="3">
+      <c r="A124" s="6">
         <v>44044</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124" s="6">
         <v>44103</v>
       </c>
-      <c r="C124" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E124" s="1">
+      <c r="C124" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E124" s="11">
         <v>0.03</v>
       </c>
-      <c r="G124" s="1">
+      <c r="G124" s="11">
         <v>-0.06</v>
       </c>
-      <c r="I124" s="2"/>
+      <c r="I124" s="4"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A125" s="3">
+      <c r="A125" s="6">
         <v>44075</v>
       </c>
-      <c r="B125" s="3">
+      <c r="B125" s="6">
         <v>44134</v>
       </c>
-      <c r="C125" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E125" s="1">
+      <c r="C125" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E125" s="11">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="G125" s="1">
+      <c r="G125" s="11">
         <v>0.03</v>
       </c>
-      <c r="I125" s="2"/>
+      <c r="I125" s="4"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A126" s="3">
+      <c r="A126" s="6">
         <v>44105</v>
       </c>
-      <c r="B126" s="3">
+      <c r="B126" s="6">
         <v>44165</v>
       </c>
-      <c r="C126" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E126" s="1">
+      <c r="C126" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E126" s="11">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="G126" s="1">
+      <c r="G126" s="11">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="I126" s="2"/>
+      <c r="I126" s="4"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A127" s="3">
+      <c r="A127" s="6">
         <v>44136</v>
       </c>
-      <c r="B127" s="3">
+      <c r="B127" s="6">
         <v>44195</v>
       </c>
-      <c r="C127" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E127" s="1">
+      <c r="C127" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E127" s="11">
         <v>-0.01</v>
       </c>
-      <c r="G127" s="1">
+      <c r="G127" s="11">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="I127" s="2"/>
+      <c r="I127" s="4"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A128" s="3">
+      <c r="A128" s="6">
         <v>44166</v>
       </c>
-      <c r="B128" s="3">
+      <c r="B128" s="6">
         <v>44225</v>
       </c>
-      <c r="C128" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E128" s="1">
+      <c r="C128" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E128" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G128" s="1">
+      <c r="G128" s="11">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="I128" s="2"/>
+      <c r="I128" s="4"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A129" s="3">
+      <c r="A129" s="6">
         <v>44197</v>
       </c>
-      <c r="B129" s="3">
+      <c r="B129" s="6">
         <v>44257</v>
       </c>
-      <c r="C129" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E129" s="1">
+      <c r="C129" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E129" s="11">
         <v>1.6E-2</v>
       </c>
-      <c r="G129" s="1">
+      <c r="G129" s="11">
         <v>1E-3</v>
       </c>
-      <c r="I129" s="2"/>
+      <c r="I129" s="4"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A130" s="3">
+      <c r="A130" s="6">
         <v>44228</v>
       </c>
-      <c r="B130" s="3">
+      <c r="B130" s="6">
         <v>44286</v>
       </c>
-      <c r="C130" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E130" s="1">
+      <c r="C130" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E130" s="11">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="G130" s="1">
+      <c r="G130" s="11">
         <v>1.6E-2</v>
       </c>
-      <c r="I130" s="2"/>
+      <c r="I130" s="4"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A131" s="3">
+      <c r="A131" s="6">
         <v>44256</v>
       </c>
-      <c r="B131" s="3">
+      <c r="B131" s="6">
         <v>44316</v>
       </c>
-      <c r="C131" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E131" s="1">
+      <c r="C131" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E131" s="11">
         <v>2.3E-2</v>
       </c>
-      <c r="G131" s="1">
+      <c r="G131" s="11">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="I131" s="2"/>
+      <c r="I131" s="4"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A132" s="3">
+      <c r="A132" s="6">
         <v>44287</v>
       </c>
-      <c r="B132" s="3">
+      <c r="B132" s="6">
         <v>44347</v>
       </c>
-      <c r="C132" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E132" s="1">
+      <c r="C132" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E132" s="11">
         <v>2.3E-2</v>
       </c>
-      <c r="G132" s="1">
+      <c r="G132" s="11">
         <v>2.3E-2</v>
       </c>
-      <c r="I132" s="2"/>
+      <c r="I132" s="4"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A133" s="3">
+      <c r="A133" s="6">
         <v>44317</v>
       </c>
-      <c r="B133" s="3">
+      <c r="B133" s="6">
         <v>44377</v>
       </c>
-      <c r="C133" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E133" s="1">
+      <c r="C133" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E133" s="11">
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="G133" s="1">
+      <c r="G133" s="11">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="I133" s="2"/>
+      <c r="I133" s="4"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A134" s="3">
+      <c r="A134" s="6">
         <v>44348</v>
       </c>
-      <c r="B134" s="3">
+      <c r="B134" s="6">
         <v>44407</v>
       </c>
-      <c r="C134" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E134" s="1">
+      <c r="C134" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E134" s="11">
         <v>1.4E-2</v>
       </c>
-      <c r="G134" s="1">
+      <c r="G134" s="11">
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="I134" s="2"/>
+      <c r="I134" s="4"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A135" s="3">
+      <c r="A135" s="6">
         <v>44378</v>
       </c>
-      <c r="B135" s="3">
+      <c r="B135" s="6">
         <v>44439</v>
       </c>
-      <c r="C135" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E135" s="1">
+      <c r="C135" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E135" s="11">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="G135" s="1">
+      <c r="G135" s="11">
         <v>1.4E-2</v>
       </c>
-      <c r="I135" s="2"/>
+      <c r="I135" s="4"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A136" s="3">
+      <c r="A136" s="6">
         <v>44409</v>
       </c>
-      <c r="B136" s="3">
+      <c r="B136" s="6">
         <v>44469</v>
       </c>
-      <c r="C136" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E136" s="1">
+      <c r="C136" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E136" s="11">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="G136" s="1">
+      <c r="G136" s="11">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="I136" s="2"/>
+      <c r="I136" s="4"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A137" s="3">
+      <c r="A137" s="6">
         <v>44440</v>
       </c>
-      <c r="B137" s="3">
+      <c r="B137" s="6">
         <v>44498</v>
       </c>
-      <c r="C137" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D137" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E137" s="1">
+      <c r="C137" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E137" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G137" s="1">
+      <c r="G137" s="11">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="I137" s="2"/>
+      <c r="I137" s="4"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A138" s="3">
+      <c r="A138" s="6">
         <v>44470</v>
       </c>
-      <c r="B138" s="3">
+      <c r="B138" s="6">
         <v>44530</v>
       </c>
-      <c r="C138" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E138" s="1">
+      <c r="C138" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E138" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G138" s="1">
+      <c r="G138" s="11">
         <v>2.4E-2</v>
       </c>
-      <c r="I138" s="2"/>
+      <c r="I138" s="4"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A139" s="3">
+      <c r="A139" s="6">
         <v>44501</v>
       </c>
-      <c r="B139" s="3">
+      <c r="B139" s="6">
         <v>44560</v>
       </c>
-      <c r="C139" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E139" s="1">
+      <c r="C139" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E139" s="11">
         <v>-1.9E-2</v>
       </c>
-      <c r="G139" s="1">
+      <c r="G139" s="11">
         <v>1E-3</v>
       </c>
-      <c r="I139" s="2"/>
+      <c r="I139" s="4"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A140" s="3">
+      <c r="A140" s="6">
         <v>44531</v>
       </c>
-      <c r="B140" s="3">
+      <c r="B140" s="6">
         <v>44589</v>
       </c>
-      <c r="C140" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E140" s="1">
+      <c r="C140" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E140" s="11">
         <v>0.02</v>
       </c>
-      <c r="G140" s="1">
+      <c r="G140" s="11">
         <v>-1.9E-2</v>
       </c>
-      <c r="I140" s="2"/>
+      <c r="I140" s="4"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A141" s="3">
+      <c r="A141" s="6">
         <v>44562</v>
       </c>
-      <c r="B141" s="3">
+      <c r="B141" s="6">
         <v>44622</v>
       </c>
-      <c r="C141" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E141" s="1">
+      <c r="C141" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E141" s="11">
         <v>-1.9E-2</v>
       </c>
-      <c r="G141" s="1">
+      <c r="G141" s="11">
         <v>0.02</v>
       </c>
-      <c r="I141" s="2"/>
+      <c r="I141" s="4"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A142" s="3">
+      <c r="A142" s="6">
         <v>44593</v>
       </c>
-      <c r="B142" s="3">
+      <c r="B142" s="6">
         <v>44651</v>
       </c>
-      <c r="C142" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E142" s="1">
+      <c r="C142" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E142" s="11">
         <v>1E-3</v>
       </c>
-      <c r="G142" s="1">
+      <c r="G142" s="11">
         <v>-1.9E-2</v>
       </c>
-      <c r="I142" s="2"/>
+      <c r="I142" s="4"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A143" s="3">
+      <c r="A143" s="6">
         <v>44621</v>
       </c>
-      <c r="B143" s="3">
+      <c r="B143" s="6">
         <v>44680</v>
       </c>
-      <c r="C143" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D143" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E143" s="1">
+      <c r="C143" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E143" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="G143" s="1">
+      <c r="G143" s="11">
         <v>1E-3</v>
       </c>
-      <c r="I143" s="2"/>
+      <c r="I143" s="4"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A144" s="3">
+      <c r="A144" s="6">
         <v>44652</v>
       </c>
-      <c r="B144" s="3">
+      <c r="B144" s="6">
         <v>44712</v>
       </c>
-      <c r="C144" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E144" s="1">
+      <c r="C144" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E144" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="G144" s="1">
+      <c r="G144" s="11">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="I144" s="2"/>
+      <c r="I144" s="4"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A145" s="3">
+      <c r="A145" s="6">
         <v>44682</v>
       </c>
-      <c r="B145" s="3">
+      <c r="B145" s="6">
         <v>44742</v>
       </c>
-      <c r="C145" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E145" s="1">
+      <c r="C145" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E145" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="G145" s="1">
+      <c r="G145" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="I145" s="2"/>
+      <c r="I145" s="4"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A146" s="3">
+      <c r="A146" s="6">
         <v>44713</v>
       </c>
-      <c r="B146" s="3">
+      <c r="B146" s="6">
         <v>44771</v>
       </c>
-      <c r="C146" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E146" s="1">
+      <c r="C146" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E146" s="11">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="G146" s="1">
+      <c r="G146" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="I146" s="2"/>
+      <c r="I146" s="4"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A147" s="3">
+      <c r="A147" s="6">
         <v>44743</v>
       </c>
-      <c r="B147" s="3">
+      <c r="B147" s="6">
         <v>44804</v>
       </c>
-      <c r="C147" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E147" s="1">
+      <c r="C147" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E147" s="11">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="G147" s="1">
+      <c r="G147" s="11">
         <v>-0.01</v>
       </c>
-      <c r="I147" s="2"/>
+      <c r="I147" s="4"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A148" s="3">
+      <c r="A148" s="6">
         <v>44774</v>
       </c>
-      <c r="B148" s="3">
+      <c r="B148" s="6">
         <v>44834</v>
       </c>
-      <c r="C148" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E148" s="1">
+      <c r="C148" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E148" s="11">
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="G148" s="1">
+      <c r="G148" s="11">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="I148" s="2"/>
+      <c r="I148" s="4"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A149" s="3">
+      <c r="A149" s="6">
         <v>44805</v>
       </c>
-      <c r="B149" s="3">
+      <c r="B149" s="6">
         <v>44865</v>
       </c>
-      <c r="C149" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E149" s="1">
+      <c r="C149" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E149" s="11">
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="G149" s="1">
+      <c r="G149" s="11">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="I149" s="2"/>
+      <c r="I149" s="4"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A150" s="3">
+      <c r="A150" s="6">
         <v>44835</v>
       </c>
-      <c r="B150" s="3">
+      <c r="B150" s="6">
         <v>44895</v>
       </c>
-      <c r="C150" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E150" s="1">
+      <c r="C150" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E150" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="G150" s="1">
+      <c r="G150" s="11">
         <v>-1.9E-2</v>
       </c>
-      <c r="I150" s="2"/>
+      <c r="I150" s="4"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A151" s="3">
+      <c r="A151" s="6">
         <v>44866</v>
       </c>
-      <c r="B151" s="3">
+      <c r="B151" s="6">
         <v>44924</v>
       </c>
-      <c r="C151" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E151" s="1">
+      <c r="C151" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E151" s="11">
         <v>-1.7999999999999999E-2</v>
       </c>
-      <c r="G151" s="1">
+      <c r="G151" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="I151" s="2"/>
+      <c r="I151" s="4"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A152" s="3">
+      <c r="A152" s="6">
         <v>44896</v>
       </c>
-      <c r="B152" s="3">
+      <c r="B152" s="6">
         <v>44957</v>
       </c>
-      <c r="C152" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E152" s="1">
+      <c r="C152" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E152" s="11">
         <v>1.4E-2</v>
       </c>
-      <c r="G152" s="1">
+      <c r="G152" s="11">
         <v>-1.7000000000000001E-2</v>
       </c>
-      <c r="I152" s="2"/>
+      <c r="I152" s="4"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A153" s="3">
+      <c r="A153" s="6">
         <v>44927</v>
       </c>
-      <c r="B153" s="3">
+      <c r="B153" s="6">
         <v>44987</v>
       </c>
-      <c r="C153" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E153" s="1">
+      <c r="C153" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E153" s="11">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="G153" s="1">
+      <c r="G153" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="I153" s="2"/>
+      <c r="I153" s="4"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A154" s="3">
+      <c r="A154" s="6">
         <v>44958</v>
       </c>
-      <c r="B154" s="3">
+      <c r="B154" s="6">
         <v>45016</v>
       </c>
-      <c r="C154" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E154" s="1">
+      <c r="C154" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E154" s="11">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="G154" s="1">
+      <c r="G154" s="11">
         <v>-1.0999999999999999E-2</v>
       </c>
-      <c r="I154" s="2"/>
+      <c r="I154" s="4"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A155" s="3">
+      <c r="A155" s="6">
         <v>44986</v>
       </c>
-      <c r="B155" s="3">
+      <c r="B155" s="6">
         <v>45044</v>
       </c>
-      <c r="C155" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E155" s="1">
+      <c r="C155" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E155" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="F155" s="1">
+      <c r="F155" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="G155" s="1">
+      <c r="G155" s="11">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="I155" s="2"/>
+      <c r="I155" s="4"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A156" s="3">
+      <c r="A156" s="6">
         <v>45017</v>
       </c>
-      <c r="B156" s="3">
+      <c r="B156" s="6">
         <v>45077</v>
       </c>
-      <c r="C156" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D156" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E156" s="1">
+      <c r="C156" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E156" s="11">
         <v>-2.3E-2</v>
       </c>
-      <c r="F156" s="1">
+      <c r="F156" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G156" s="1">
+      <c r="G156" s="11">
         <v>1E-3</v>
       </c>
-      <c r="I156" s="2"/>
+      <c r="I156" s="4"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A157" s="3">
+      <c r="A157" s="6">
         <v>45047</v>
       </c>
-      <c r="B157" s="3">
+      <c r="B157" s="6">
         <v>45107</v>
       </c>
-      <c r="C157" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E157" s="1">
+      <c r="C157" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E157" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="F157" s="1">
+      <c r="F157" s="11">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="G157" s="1">
+      <c r="G157" s="11">
         <v>-2.5999999999999999E-2</v>
       </c>
-      <c r="I157" s="2"/>
+      <c r="I157" s="4"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A158" s="3">
+      <c r="A158" s="6">
         <v>45078</v>
       </c>
-      <c r="B158" s="3">
+      <c r="B158" s="6">
         <v>45135</v>
       </c>
-      <c r="C158" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D158" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E158" s="1">
+      <c r="C158" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E158" s="11">
         <v>0.01</v>
       </c>
-      <c r="F158" s="1">
+      <c r="F158" s="11">
         <v>0</v>
       </c>
-      <c r="G158" s="1">
+      <c r="G158" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="I158" s="2"/>
+      <c r="I158" s="4"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A159" s="3">
+      <c r="A159" s="6">
         <v>45108</v>
       </c>
-      <c r="B159" s="3">
+      <c r="B159" s="6">
         <v>45169</v>
       </c>
-      <c r="C159" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D159" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E159" s="1">
+      <c r="C159" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E159" s="11">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="F159" s="1">
+      <c r="F159" s="11">
         <v>0</v>
       </c>
-      <c r="G159" s="1">
+      <c r="G159" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="I159" s="2"/>
+      <c r="I159" s="4"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A160" s="3">
+      <c r="A160" s="6">
         <v>45139</v>
       </c>
-      <c r="B160" s="3">
+      <c r="B160" s="6">
         <v>45203</v>
       </c>
-      <c r="C160" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D160" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E160" s="1">
+      <c r="C160" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E160" s="11">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="G160" s="1">
+      <c r="G160" s="11">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="I160" s="2"/>
+      <c r="I160" s="4"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A161" s="3">
+      <c r="A161" s="6">
         <v>45170</v>
       </c>
-      <c r="B161" s="3">
+      <c r="B161" s="6">
         <v>45230</v>
       </c>
-      <c r="C161" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D161" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E161" s="1">
+      <c r="C161" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E161" s="11">
         <v>2E-3</v>
       </c>
-      <c r="G161" s="1">
+      <c r="G161" s="11">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="I161" s="2"/>
+      <c r="I161" s="4"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A162" s="3">
+      <c r="A162" s="6">
         <v>45200</v>
       </c>
-      <c r="B162" s="3">
+      <c r="B162" s="6">
         <v>45260</v>
       </c>
-      <c r="C162" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D162" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E162" s="1">
+      <c r="C162" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E162" s="11">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="G162" s="1">
+      <c r="G162" s="11">
         <v>1E-3</v>
       </c>
-      <c r="I162" s="2"/>
+      <c r="I162" s="4"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A163" s="3">
+      <c r="A163" s="6">
         <v>45231</v>
       </c>
-      <c r="B163" s="3">
+      <c r="B163" s="6">
         <v>45288</v>
       </c>
-      <c r="C163" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D163" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E163" s="1">
+      <c r="C163" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E163" s="11">
         <v>0.01</v>
       </c>
-      <c r="G163" s="1">
+      <c r="G163" s="11">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="I163" s="2"/>
+      <c r="I163" s="4"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A164" s="3">
+      <c r="A164" s="6">
         <v>45261</v>
       </c>
-      <c r="B164" s="3">
+      <c r="B164" s="6">
         <v>45322</v>
       </c>
-      <c r="C164" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D164" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E164" s="1">
+      <c r="C164" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E164" s="11">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="G164" s="1">
+      <c r="G164" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="I164" s="2"/>
+      <c r="I164" s="4"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A165" s="3">
+      <c r="A165" s="6">
         <v>45292</v>
       </c>
-      <c r="B165" s="3">
+      <c r="B165" s="6">
         <v>45355</v>
       </c>
-      <c r="C165" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D165" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E165" s="1">
+      <c r="C165" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E165" s="11">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="G165" s="1">
+      <c r="G165" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I165" s="2"/>
+      <c r="I165" s="4"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A166" s="3">
+      <c r="A166" s="6">
         <v>45323</v>
       </c>
-      <c r="B166" s="3">
+      <c r="B166" s="6">
         <v>45380</v>
       </c>
-      <c r="C166" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D166" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E166" s="1">
+      <c r="C166" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E166" s="11">
         <v>-3.1E-2</v>
       </c>
-      <c r="G166" s="1">
+      <c r="G166" s="11">
         <v>0.01</v>
       </c>
-      <c r="I166" s="2"/>
+      <c r="I166" s="4"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A167" s="3">
+      <c r="A167" s="6">
         <v>45352</v>
       </c>
-      <c r="B167" s="3">
+      <c r="B167" s="6">
         <v>45412</v>
       </c>
-      <c r="C167" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D167" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E167" s="1">
+      <c r="C167" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E167" s="11">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G167" s="1">
+      <c r="G167" s="11">
         <v>-0.03</v>
       </c>
-      <c r="I167" s="2"/>
+      <c r="I167" s="4"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A168" s="3">
+      <c r="A168" s="6">
         <v>45383</v>
       </c>
-      <c r="B168" s="3">
+      <c r="B168" s="6">
         <v>45443</v>
       </c>
-      <c r="C168" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D168" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E168" s="1">
+      <c r="C168" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E168" s="11">
         <v>-1.2E-2</v>
       </c>
-      <c r="G168" s="1">
+      <c r="G168" s="11">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="I168" s="2"/>
+      <c r="I168" s="4"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A169" s="3">
+      <c r="A169" s="6">
         <v>45413</v>
       </c>
-      <c r="B169" s="3">
+      <c r="B169" s="6">
         <v>45471</v>
       </c>
-      <c r="C169" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D169" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E169" s="1">
+      <c r="C169" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E169" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="G169" s="1">
+      <c r="G169" s="11">
         <v>-1.2E-2</v>
       </c>
-      <c r="I169" s="2"/>
+      <c r="I169" s="4"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A170" s="3">
+      <c r="A170" s="6">
         <v>45444</v>
       </c>
-      <c r="B170" s="3">
+      <c r="B170" s="6">
         <v>45504</v>
       </c>
-      <c r="C170" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D170" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E170" s="1">
+      <c r="C170" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E170" s="11">
         <v>0.01</v>
       </c>
-      <c r="G170" s="1">
+      <c r="G170" s="11">
         <v>-2E-3</v>
       </c>
-      <c r="I170" s="2"/>
+      <c r="I170" s="4"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A171" s="3">
+      <c r="A171" s="6">
         <v>45474</v>
       </c>
-      <c r="B171" s="3">
+      <c r="B171" s="6">
         <v>45534</v>
       </c>
-      <c r="C171" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D171" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E171" s="1">
+      <c r="C171" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E171" s="11">
         <v>-1.9E-2</v>
       </c>
-      <c r="G171" s="1">
+      <c r="G171" s="11">
         <v>0.01</v>
       </c>
-      <c r="I171" s="2"/>
+      <c r="I171" s="4"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A172" s="3">
+      <c r="A172" s="6">
         <v>45505</v>
       </c>
-      <c r="B172" s="3">
+      <c r="B172" s="6">
         <v>45565</v>
       </c>
-      <c r="C172" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D172" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E172" s="1">
+      <c r="C172" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E172" s="11">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="G172" s="1">
+      <c r="G172" s="11">
         <v>-0.02</v>
       </c>
-      <c r="I172" s="2"/>
+      <c r="I172" s="4"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A173" s="3">
+      <c r="A173" s="6">
         <v>45536</v>
       </c>
-      <c r="B173" s="3">
+      <c r="B173" s="6">
         <v>45596</v>
       </c>
-      <c r="C173" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D173" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E173" s="1">
+      <c r="C173" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E173" s="11">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="G173" s="1">
+      <c r="G173" s="11">
         <v>1.7000000000000001E-2</v>
       </c>
-      <c r="I173" s="2"/>
+      <c r="I173" s="4"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A174" s="3">
+      <c r="A174" s="6">
         <v>45566</v>
       </c>
-      <c r="B174" s="3">
+      <c r="B174" s="6">
         <v>45625</v>
       </c>
-      <c r="C174" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E174" s="1">
+      <c r="C174" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E174" s="11">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="G174" s="1">
+      <c r="G174" s="11">
         <v>-5.0000000000000001E-3</v>
       </c>
-      <c r="I174" s="2"/>
+      <c r="I174" s="4"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A175" s="3">
+      <c r="A175" s="6">
         <v>45597</v>
       </c>
-      <c r="B175" s="3">
+      <c r="B175" s="6">
         <v>45656</v>
       </c>
-      <c r="C175" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D175" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E175" s="1">
+      <c r="C175" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E175" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="G175" s="1">
+      <c r="G175" s="11">
         <v>-8.0000000000000002E-3</v>
       </c>
-      <c r="I175" s="2"/>
+      <c r="I175" s="4"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A176" s="3">
+      <c r="A176" s="6">
         <v>45627</v>
       </c>
-      <c r="B176" s="3">
+      <c r="B176" s="6">
         <v>45691</v>
       </c>
-      <c r="C176" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D176" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E176" s="1">
+      <c r="C176" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E176" s="11">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="G176" s="1">
+      <c r="G176" s="11">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="I176" s="2"/>
+      <c r="I176" s="4"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A177" s="3">
+      <c r="A177" s="6">
         <v>45658</v>
       </c>
-      <c r="B177" s="3">
+      <c r="B177" s="6">
         <v>45720</v>
       </c>
-      <c r="C177" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D177" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E177" s="1">
+      <c r="C177" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E177" s="11">
         <v>-6.0000000000000001E-3</v>
       </c>
-      <c r="G177" s="1">
+      <c r="G177" s="11">
         <v>2E-3</v>
       </c>
-      <c r="I177" s="2"/>
+      <c r="I177" s="4"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A178" s="3">
+      <c r="A178" s="6">
         <v>45689</v>
       </c>
-      <c r="B178" s="3">
+      <c r="B178" s="6">
         <v>45747</v>
       </c>
-      <c r="C178" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D178" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E178" s="1">
+      <c r="C178" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E178" s="11">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="G178" s="1">
+      <c r="G178" s="11">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="I178" s="2"/>
+      <c r="I178" s="4"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A179" s="3">
+      <c r="A179" s="6">
         <v>45717</v>
       </c>
-      <c r="B179" s="3">
+      <c r="B179" s="6">
         <v>45777</v>
       </c>
-      <c r="C179" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D179" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E179" s="1">
+      <c r="C179" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E179" s="11">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="G179" s="1">
+      <c r="G179" s="11">
         <v>1.9E-2</v>
       </c>
-      <c r="I179" s="2"/>
+      <c r="I179" s="4"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A180" s="3">
+      <c r="A180" s="6">
         <v>45748</v>
       </c>
-      <c r="B180" s="3">
+      <c r="B180" s="6">
         <v>45807</v>
       </c>
-      <c r="C180" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D180" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E180" s="1">
+      <c r="C180" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E180" s="11">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="G180" s="1">
+      <c r="G180" s="11">
         <v>-0.01</v>
       </c>
-      <c r="I180" s="2"/>
+      <c r="I180" s="4"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A181" s="3">
+      <c r="A181" s="6">
         <v>45778</v>
       </c>
-      <c r="B181" s="3">
+      <c r="B181" s="6">
         <v>45838</v>
       </c>
-      <c r="C181" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D181" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E181" s="1">
+      <c r="C181" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E181" s="11">
         <v>0</v>
       </c>
-      <c r="F181" s="1">
+      <c r="F181" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="G181" s="1">
+      <c r="G181" s="11">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="I181" s="2"/>
+      <c r="I181" s="4"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A182" s="3">
+      <c r="A182" s="6">
         <v>45809</v>
       </c>
-      <c r="B182" s="3">
+      <c r="B182" s="6">
         <v>45869</v>
       </c>
-      <c r="C182" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D182" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E182" s="1">
+      <c r="C182" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E182" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G182" s="1">
+      <c r="G182" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="I182" s="2"/>
+      <c r="I182" s="4"/>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A183" s="3">
+      <c r="A183" s="6">
         <v>45839</v>
       </c>
-      <c r="B183" s="3">
+      <c r="B183" s="6">
         <v>45898</v>
       </c>
-      <c r="C183" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D183" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E183" s="1">
+      <c r="C183" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D183" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E183" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="G183" s="1">
+      <c r="G183" s="11">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="I183" s="2"/>
+      <c r="I183" s="4"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A184" s="3">
+      <c r="A184" s="6">
         <v>45870</v>
       </c>
-      <c r="B184" s="3">
+      <c r="B184" s="6">
         <v>45930</v>
       </c>
-      <c r="C184" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D184" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E184" s="1">
+      <c r="C184" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E184" s="11">
         <v>-2.4E-2</v>
       </c>
-      <c r="G184" s="1">
+      <c r="G184" s="11">
         <v>2.7E-2</v>
       </c>
-      <c r="I184" s="2"/>
+      <c r="I184" s="4"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A185" s="3">
+      <c r="A185" s="6">
         <v>45901</v>
       </c>
-      <c r="B185" s="3">
+      <c r="B185" s="6">
         <v>45961</v>
       </c>
-      <c r="C185" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D185" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E185" s="1">
+      <c r="C185" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E185" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="G185" s="1">
+      <c r="G185" s="11">
         <v>-2.4E-2</v>
       </c>
-      <c r="I185" s="2"/>
+      <c r="I185" s="4"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A186" s="3">
+      <c r="A186" s="6">
         <v>45931</v>
       </c>
-      <c r="B186" s="3">
+      <c r="B186" s="6">
         <v>45989</v>
       </c>
-      <c r="C186" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D186" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E186" s="1">
+      <c r="C186" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E186" s="11">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G186" s="1">
+      <c r="G186" s="11">
         <v>-1E-3</v>
       </c>
-      <c r="I186" s="2"/>
+      <c r="I186" s="4"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A187" s="3">
+      <c r="A187" s="6">
         <v>45962</v>
       </c>
-      <c r="B187" s="3">
+      <c r="B187" s="6">
         <v>46021</v>
       </c>
-      <c r="C187" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D187" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E187" s="1">
+      <c r="C187" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E187" s="11">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="G187" s="1">
+      <c r="G187" s="11">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="I187" s="2"/>
+      <c r="I187" s="4"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A188" s="3">
+      <c r="A188" s="6">
         <v>45992</v>
       </c>
-      <c r="B188" s="3">
+      <c r="B188" s="6">
         <v>46052</v>
       </c>
-      <c r="C188" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D188" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E188" s="1">
+      <c r="C188" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E188" s="11">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="G188" s="1">
+      <c r="G188" s="11">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="I188" s="2"/>
+      <c r="I188" s="4"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A189" s="3">
+      <c r="A189" s="6">
         <v>46023</v>
       </c>
-      <c r="B189" s="3">
+      <c r="B189" s="6">
         <v>46085</v>
       </c>
-      <c r="C189" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D189" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E189" s="1">
+      <c r="C189" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E189" s="11">
         <v>2.3E-2</v>
       </c>
-      <c r="G189" s="1">
+      <c r="G189" s="11">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I189" s="2"/>
+      <c r="I189" s="4"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A190" s="3">
+      <c r="A190" s="6">
         <v>46054</v>
       </c>
-      <c r="B190" s="3">
+      <c r="B190" s="6">
         <v>46112</v>
       </c>
-      <c r="C190" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D190" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E190" s="1">
+      <c r="C190" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E190" s="11">
         <v>0</v>
       </c>
-      <c r="G190" s="1">
+      <c r="G190" s="11">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="I190" s="2"/>
+      <c r="I190" s="4"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A191" s="3">
+      <c r="A191" s="6">
         <v>46082</v>
       </c>
-      <c r="B191" s="3">
+      <c r="B191" s="6">
         <v>46142</v>
       </c>
-      <c r="C191" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D191" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E191" s="1">
+      <c r="C191" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E191" s="11">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="G191" s="1">
+      <c r="G191" s="11">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="I191" s="2"/>
+      <c r="I191" s="4"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A192" s="3">
+      <c r="A192" s="6">
         <v>46113</v>
       </c>
-      <c r="B192" s="3">
+      <c r="B192" s="6">
         <v>46171</v>
       </c>
-      <c r="C192" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D192" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E192" s="1">
+      <c r="C192" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D192" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E192" s="11">
         <v>-3.5999999999999997E-2</v>
       </c>
-      <c r="G192" s="1">
+      <c r="G192" s="11">
         <v>1.9E-2</v>
       </c>
-      <c r="I192" s="2"/>
+      <c r="I192" s="4"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A193" s="3">
+      <c r="A193" s="6">
         <v>46143</v>
       </c>
-      <c r="B193" s="3">
+      <c r="B193" s="6">
         <v>46203</v>
       </c>
-      <c r="C193" s="6">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="D193" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G193" s="1">
-        <v>-3.5999999999999997E-2</v>
-      </c>
-      <c r="I193" s="2"/>
+      <c r="C193" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E193" s="11">
+        <v>1E-3</v>
+      </c>
+      <c r="G193" s="11">
+        <v>-3.5000000000000003E-2</v>
+      </c>
+      <c r="I193" s="4"/>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A194" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B194" s="6">
+        <v>46234</v>
+      </c>
+      <c r="C194" s="7">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E194" s="11">
+        <v>2.7E-2</v>
+      </c>
+      <c r="G194" s="11">
+        <v>1E-3</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G193">
     <sortCondition ref="B2:B193"/>
   </sortState>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>